--- a/outputs_xlsx_solution/prog-noloop.4-wide.xlsx
+++ b/outputs_xlsx_solution/prog-noloop.4-wide.xlsx
@@ -77,7 +77,10 @@
     <t>fsd F0, 0(X2)</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
   <si>
     <t>addi X1, X1, -8</t>
@@ -86,10 +89,10 @@
     <t>addi X2, X2, -8</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
   </si>
   <si>
     <t>[Legend]</t>
@@ -101,13 +104,34 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -534,7 +558,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -557,10 +581,10 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -583,10 +607,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -606,13 +630,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -632,22 +656,22 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -667,16 +691,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
         <v>18</v>
       </c>
-      <c r="I7" t="s">
-        <v>17</v>
-      </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -696,19 +720,19 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -728,13 +752,13 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +769,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -757,10 +781,10 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -771,7 +795,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -783,18 +807,18 @@
         <v>14</v>
       </c>
       <c r="I11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
         <v>18</v>
       </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
       <c r="P11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +826,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -810,31 +834,55 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/prog-noloop.4-wide.xlsx
+++ b/outputs_xlsx_solution/prog-noloop.4-wide.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -132,6 +135,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -558,7 +564,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +584,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -607,10 +613,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -630,13 +636,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -656,7 +662,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -671,7 +677,7 @@
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -691,16 +697,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -720,7 +726,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
@@ -732,7 +738,7 @@
         <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -752,13 +758,13 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O9" t="s">
         <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -769,7 +775,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -781,10 +787,10 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -795,7 +801,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -804,21 +810,21 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -834,15 +840,15 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -850,39 +856,55 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
         <v>31</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
         <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
